--- a/ESM_23.xlsx
+++ b/ESM_23.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\University of Dayton\Reseach in UD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Reseach in UD\A-Surrogate-Model-for-Laser-Based-Powder-Bed-Fusion-of-Metals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5031750-FA53-4B9F-AC6F-3FBABFEB089A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60248040-0221-4A6F-9EEB-B6FE694103C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{46BB7AF0-E513-47EB-8CBC-6F900FBE8403}"/>
   </bookViews>
@@ -226,8 +226,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="96500" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -269,6 +269,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMath>
@@ -287,7 +288,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -760,13 +761,13 @@
         <v>7.4999999999999993E-5</v>
       </c>
       <c r="J2" s="5">
-        <v>4.3999999999999999E-5</v>
+        <v>4.5000000000000003E-5</v>
       </c>
       <c r="K2" s="5">
         <v>1.3999999999999999E-4</v>
       </c>
       <c r="L2" s="6">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="M2" s="6" t="s">
         <v>23</v>
@@ -816,25 +817,25 @@
         <v>8.5000000000000006E-5</v>
       </c>
       <c r="J3" s="5">
-        <v>6.4999999999999994E-5</v>
+        <v>6.0000000000000002E-5</v>
       </c>
       <c r="K3" s="5">
         <v>4.0000000000000003E-5</v>
       </c>
       <c r="L3" s="6">
-        <v>0.26</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="M3" s="5">
-        <v>6.0000000000000002E-5</v>
+        <v>5.0000000000000002E-5</v>
       </c>
       <c r="N3" s="5">
-        <v>4.0000000000000003E-5</v>
+        <v>3.4999999999999997E-5</v>
       </c>
       <c r="O3" s="5">
-        <v>1.4200000000000001E-4</v>
+        <v>1.3999999999999999E-4</v>
       </c>
       <c r="P3" s="6">
-        <v>0.375</v>
+        <v>0.33</v>
       </c>
       <c r="Q3" s="6">
         <v>5</v>
@@ -872,13 +873,13 @@
         <v>7.4999999999999993E-5</v>
       </c>
       <c r="J4" s="5">
-        <v>4.3999999999999999E-5</v>
+        <v>4.5000000000000003E-5</v>
       </c>
       <c r="K4" s="5">
         <v>1.3999999999999999E-4</v>
       </c>
       <c r="L4" s="6">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="M4" s="6" t="s">
         <v>23</v>
@@ -928,25 +929,25 @@
         <v>8.5000000000000006E-5</v>
       </c>
       <c r="J5" s="5">
-        <v>6.4999999999999994E-5</v>
+        <v>6.0000000000000002E-5</v>
       </c>
       <c r="K5" s="5">
         <v>4.0000000000000003E-5</v>
       </c>
       <c r="L5" s="6">
-        <v>0.26</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="M5" s="5">
-        <v>6.0000000000000002E-5</v>
+        <v>5.0000000000000002E-5</v>
       </c>
       <c r="N5" s="5">
-        <v>4.0000000000000003E-5</v>
+        <v>3.4999999999999997E-5</v>
       </c>
       <c r="O5" s="5">
-        <v>1.4200000000000001E-4</v>
+        <v>1.3999999999999999E-4</v>
       </c>
       <c r="P5" s="6">
-        <v>0.375</v>
+        <v>0.33</v>
       </c>
       <c r="Q5" s="6">
         <v>5</v>

--- a/ESM_23.xlsx
+++ b/ESM_23.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Reseach in UD\A-Surrogate-Model-for-Laser-Based-Powder-Bed-Fusion-of-Metals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60248040-0221-4A6F-9EEB-B6FE694103C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15143C6D-3EED-4203-9C7E-E81E0EE17B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{46BB7AF0-E513-47EB-8CBC-6F900FBE8403}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{46BB7AF0-E513-47EB-8CBC-6F900FBE8403}"/>
   </bookViews>
   <sheets>
     <sheet name="All parameters" sheetId="1" r:id="rId1"/>
@@ -671,7 +671,7 @@
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.77734375" customWidth="1"/>
     <col min="6" max="7" width="8.109375" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" customWidth="1"/>
